--- a/XFL Log/Experiment Log.xlsx
+++ b/XFL Log/Experiment Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XFLControlSystem\Documents\GitHub\XFL\XFL Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B89259-9D59-471C-B60A-8198F066B68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65450DA2-8F70-4CD0-BD64-FDB46AFF2DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="1290" windowWidth="21600" windowHeight="11385" xr2:uid="{4D1BEA23-A2B2-4E44-BBEF-61E195E37D61}"/>
+    <workbookView xWindow="4980" yWindow="5175" windowWidth="21600" windowHeight="11385" xr2:uid="{4D1BEA23-A2B2-4E44-BBEF-61E195E37D61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -63,16 +63,34 @@
   </si>
   <si>
     <t>Sequence - 2024-09-24 - Long</t>
+  </si>
+  <si>
+    <t>HDF2003</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>0.54 L/s IV Flow Rate</t>
+  </si>
+  <si>
+    <t>1 L/s IV Flow Rate, Multi Run</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -113,7 +131,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -151,15 +172,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BCEE4A8-6C1E-4C6C-9834-80122D9F3F78}" name="Table1" displayName="Table1" ref="A1:F4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:F4" xr:uid="{2BCEE4A8-6C1E-4C6C-9834-80122D9F3F78}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E9218278-0206-4926-AF74-CCB7F589E780}" name="Date" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{08AE4FC0-CB7F-4B55-8463-9618B60FC76F}" name="Time" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{1E31CE90-93DC-4B85-B130-0F4E3BE68681}" name="Fluid Medium" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{8C8A0010-2BCB-4CDF-B060-5F76C860F7DF}" name="Pump Inlet Pressure (Bar)" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{D4CA714A-896F-4B27-9F7A-10CE83252E82}" name="Temperature" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BCEE4A8-6C1E-4C6C-9834-80122D9F3F78}" name="Table1" displayName="Table1" ref="A1:G6" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:G6" xr:uid="{2BCEE4A8-6C1E-4C6C-9834-80122D9F3F78}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E9218278-0206-4926-AF74-CCB7F589E780}" name="Date" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{08AE4FC0-CB7F-4B55-8463-9618B60FC76F}" name="Time" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{1E31CE90-93DC-4B85-B130-0F4E3BE68681}" name="Fluid Medium" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{8C8A0010-2BCB-4CDF-B060-5F76C860F7DF}" name="Pump Inlet Pressure (Bar)" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{D4CA714A-896F-4B27-9F7A-10CE83252E82}" name="Temperature" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{E30C2E14-1FD9-4B0B-83DD-60D74B5BFE71}" name="Sequence"/>
+    <tableColumn id="7" xr3:uid="{1C36B364-C3F3-4AE0-97F9-78919E1A2ABB}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -482,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D085CF-3575-4C7A-95E1-7B317E178279}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -491,9 +513,10 @@
     <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,8 +535,11 @@
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45559</v>
       </c>
@@ -532,8 +558,9 @@
       <c r="F2" t="s">
         <v>7</v>
       </c>
+      <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45559</v>
       </c>
@@ -552,8 +579,9 @@
       <c r="F3" t="s">
         <v>7</v>
       </c>
+      <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45559</v>
       </c>
@@ -572,8 +600,56 @@
       <c r="F4" t="s">
         <v>8</v>
       </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45560</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.48125000000000001</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.755</v>
+      </c>
+      <c r="E5" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45560</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.48125000000000001</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.755</v>
+      </c>
+      <c r="E6" s="1">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
